--- a/tools/issue-log-agent/templates/Template_Backlog_v2.xlsx
+++ b/tools/issue-log-agent/templates/Template_Backlog_v2.xlsx
@@ -1,16 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
-    <sheet name="FEATURE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="BUG" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SECURITY" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PERFORMANCE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FEATURE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUG" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SECURITY" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERFORMANCE" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,62 +16,93 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FFA61C00"/>
+        <bgColor rgb="FFA61C00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="007F7F7F"/>
+        <fgColor rgb="FFFF9900"/>
+        <bgColor rgb="FFFF9900"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF351C75"/>
+        <bgColor rgb="FF351C75"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A86E8"/>
+        <bgColor rgb="FF4A86E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF666666"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -147,115 +174,346 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Issue Backlog Agent</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Judul tanpa prefix. Prefix [FEATURE][SOURCE]- ditambahkan otomatis.
+Jika kosong dan fitur Claude aktif, agent membuatkan judul untuk dicek.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib. Pilih: FSD, BRD, INT</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib diisi.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib diisi.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib diisi.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Pilih: Open, On-Progress, Testing, Re-work, Ready to Deploy, Closed. Kosong = Open.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Issue Backlog Agent</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Judul tanpa prefix. Prefix [BUG][SOURCE]- ditambahkan otomatis.
+Jika kosong dan fitur Claude aktif, agent membuatkan judul untuk dicek.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib. Pilih: VIT, SIT, UAT</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib diisi.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib diisi.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib diisi.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib diisi.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib diisi.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib diisi.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Pilih: Open, On-Progress, Testing, Re-work, Ready to Deploy, Closed. Kosong = Open.</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Issue Backlog Agent</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Judul tanpa prefix. Prefix [SECURITY][SOURCE]- ditambahkan otomatis.
+Jika kosong dan fitur Claude aktif, agent membuatkan judul untuk dicek.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib. Pilih: EXT, INT</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib diisi.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib diisi.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib diisi.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib diisi.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Pilih: Open, On-Progress, Testing, Re-work, Ready to Deploy, Closed. Kosong = Open.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Issue Backlog Agent</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Judul tanpa prefix. Prefix [PERFORMANCE][SOURCE]- ditambahkan otomatis.
+Jika kosong dan fitur Claude aktif, agent membuatkan judul untuk dicek.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib. Pilih: EXT, INT</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib diisi.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib diisi.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib diisi.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Wajib diisi.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Pilih: Open, On-Progress, Testing, Re-work, Ready to Deploy, Closed. Kosong = Open.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>Diisi otomatis oleh agent. Jangan diubah.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -267,273 +525,243 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <tabColor rgb="FF4A86E8"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="45" customWidth="1" style="5" min="1" max="7"/>
+    <col width="12" customWidth="1" style="5" min="2" max="2"/>
+    <col width="27" customWidth="1" style="5" min="3" max="3"/>
+    <col width="27" customWidth="1" style="5" min="4" max="4"/>
+    <col width="27" customWidth="1" style="5" min="5" max="5"/>
+    <col width="27" customWidth="1" style="5" min="6" max="6"/>
+    <col width="27" customWidth="1" style="5" min="7" max="7"/>
+    <col width="27" customWidth="1" style="5" min="8" max="8"/>
+    <col width="27" customWidth="1" style="5" min="9" max="9"/>
+    <col width="27" customWidth="1" style="5" min="10" max="10"/>
+    <col width="18" customWidth="1" style="5" min="11" max="11"/>
+    <col width="18" customWidth="1" style="5" min="12" max="12"/>
+    <col width="18" customWidth="1" style="5" min="13" max="13"/>
+    <col width="18" customWidth="1" style="5" min="14" max="14"/>
+    <col width="18" customWidth="1" style="5" min="15" max="15"/>
+    <col width="18" customWidth="1" style="5" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="31.5" customHeight="1" s="5">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Source *</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Background *</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Description *</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Background</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Business / Functional Requirement</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria *</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Technical Notes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Out of Scope</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Issue Board Status</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>GitLab Issue</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>GitLab URL</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Sync Status</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Sync Message</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>Synced At</t>
         </is>
@@ -541,47 +769,49 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Source" error="Pilih salah satu: FSD, BRD, INT" type="list">
       <formula1>"FSD,BRD,INT"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Issue Board Status" error="Pilih salah satu: Open, On-Progress, Testing, Re-work, Ready to Deploy, Closed" type="list">
       <formula1>"Open,On-Progress,Testing,Re-work,Ready to Deploy,Closed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <tabColor rgb="FF980000"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="32" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="45" customWidth="1" style="5" min="1" max="9"/>
+    <col width="12" customWidth="1" style="5" min="2" max="2"/>
+    <col width="27" customWidth="1" style="5" min="3" max="3"/>
+    <col width="27" customWidth="1" style="5" min="4" max="4"/>
+    <col width="27" customWidth="1" style="5" min="5" max="5"/>
+    <col width="27" customWidth="1" style="5" min="6" max="6"/>
+    <col width="27" customWidth="1" style="5" min="7" max="7"/>
+    <col width="27" customWidth="1" style="5" min="8" max="8"/>
+    <col width="27" customWidth="1" style="5" min="9" max="9"/>
+    <col width="27" customWidth="1" style="5" min="10" max="10"/>
+    <col width="27" customWidth="1" style="5" min="11" max="11"/>
+    <col width="27" customWidth="1" style="5" min="12" max="12"/>
+    <col width="18" customWidth="1" style="5" min="13" max="13"/>
+    <col width="18" customWidth="1" style="5" min="14" max="14"/>
+    <col width="18" customWidth="1" style="5" min="15" max="15"/>
+    <col width="18" customWidth="1" style="5" min="16" max="16"/>
+    <col width="18" customWidth="1" style="5" min="17" max="17"/>
+    <col width="18" customWidth="1" style="5" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="31.5" customHeight="1" s="5">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
@@ -589,12 +819,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Source *</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Background *</t>
+          <t>Background</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -604,22 +834,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Environment *</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Steps to Reproduce *</t>
+          <t>Steps to Reproduce</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Expected Result *</t>
+          <t>Expected Result</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Actual Result *</t>
+          <t>Actual Result</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -629,7 +859,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Acceptance Criteria *</t>
+          <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -647,27 +877,27 @@
           <t>Issue Board Status</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>GitLab Issue</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>GitLab URL</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>Sync Status</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>Sync Message</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="R1" s="6" t="inlineStr">
         <is>
           <t>Synced At</t>
         </is>
@@ -675,103 +905,105 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Source" error="Pilih salah satu: VIT, SIT, UAT" type="list">
       <formula1>"VIT,SIT,UAT"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Issue Board Status" error="Pilih salah satu: Open, On-Progress, Testing, Re-work, Ready to Deploy, Closed" type="list">
       <formula1>"Open,On-Progress,Testing,Re-work,Ready to Deploy,Closed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <tabColor rgb="FFFF9900"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" style="5" min="1" max="5"/>
+    <col width="12" customWidth="1" style="5" min="2" max="2"/>
+    <col width="27" customWidth="1" style="5" min="3" max="3"/>
+    <col width="27" customWidth="1" style="5" min="4" max="4"/>
+    <col width="27" customWidth="1" style="5" min="5" max="5"/>
+    <col width="27" customWidth="1" style="5" min="6" max="6"/>
+    <col width="27" customWidth="1" style="5" min="7" max="7"/>
+    <col width="18" customWidth="1" style="5" min="8" max="8"/>
+    <col width="18" customWidth="1" style="5" min="9" max="9"/>
+    <col width="18" customWidth="1" style="5" min="10" max="10"/>
+    <col width="18" customWidth="1" style="5" min="11" max="11"/>
+    <col width="18" customWidth="1" style="5" min="12" max="12"/>
+    <col width="18" customWidth="1" style="5" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="31.5" customHeight="1" s="5">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Source *</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Description *</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Impact *</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Recommendation *</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria *</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Evidence / Reference</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Issue Board Status</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>GitLab Issue</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>GitLab URL</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Sync Status</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Sync Message</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Synced At</t>
         </is>
@@ -779,115 +1011,117 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Source" error="Pilih salah satu: EXT, INT" type="list">
       <formula1>"EXT,INT"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Issue Board Status" error="Pilih salah satu: Open, On-Progress, Testing, Re-work, Ready to Deploy, Closed" type="list">
       <formula1>"Open,On-Progress,Testing,Re-work,Ready to Deploy,Closed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <tabColor rgb="FF674EA7"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="45" customWidth="1" style="5" min="1" max="5"/>
+    <col width="12" customWidth="1" style="5" min="2" max="2"/>
+    <col width="27" customWidth="1" style="5" min="3" max="3"/>
+    <col width="27" customWidth="1" style="5" min="4" max="4"/>
+    <col width="27" customWidth="1" style="5" min="5" max="5"/>
+    <col width="27" customWidth="1" style="5" min="6" max="6"/>
+    <col width="27" customWidth="1" style="5" min="7" max="7"/>
+    <col width="27" customWidth="1" style="5" min="8" max="8"/>
+    <col width="27" customWidth="1" style="5" min="9" max="9"/>
+    <col width="18" customWidth="1" style="5" min="10" max="10"/>
+    <col width="18" customWidth="1" style="5" min="11" max="11"/>
+    <col width="18" customWidth="1" style="5" min="12" max="12"/>
+    <col width="18" customWidth="1" style="5" min="13" max="13"/>
+    <col width="18" customWidth="1" style="5" min="14" max="14"/>
+    <col width="18" customWidth="1" style="5" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="31.5" customHeight="1" s="5">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Source *</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Description *</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Current Condition *</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Condition *</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Current Condition</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Expected Condition</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria *</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Evidence / Reference</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Issue Board Status</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>GitLab Issue</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>GitLab URL</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Sync Status</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Sync Message</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Synced At</t>
         </is>
@@ -895,13 +1129,14 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Source" error="Pilih salah satu: EXT, INT" type="list">
       <formula1>"EXT,INT"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Issue Board Status" error="Pilih salah satu: Open, On-Progress, Testing, Re-work, Ready to Deploy, Closed" type="list">
       <formula1>"Open,On-Progress,Testing,Re-work,Ready to Deploy,Closed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>